--- a/output/HS_Code_Summary_EL_GAUCHO_CZ_GAUCHO05.xlsx
+++ b/output/HS_Code_Summary_EL_GAUCHO_CZ_GAUCHO05.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -649,31 +649,31 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3924 10 00</t>
+          <t>3924 10 00 19</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Big tray; Bread plate; Chimichurri cup; Peanut bowl; Caviar spoon</t>
+          <t>Bread plate; Chimichurri cup; Peanut bowl</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Velký plastový servírovací podnos; Melaminový talířek na chléb; Melaminová miska na chimichurri; Melaminová miska na arašídy; Lžička na kaviár</t>
+          <t>Talíř na chléb, kulatý černý, melamin; Miska na chimichurri, melamin; Miska na arašídy, melamin</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>20, 26, 48, 63, 64</t>
+          <t>26, 48, 63</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Melanine, Plastic</t>
+          <t>Melanine</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1836</v>
+        <v>1800</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>251.04</v>
+        <v>223</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>1738.8</v>
+        <v>1290</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
@@ -710,22 +710,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3926 90 97</t>
+          <t>3924 10 00 90</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Pin</t>
+          <t>Big tray; Caviar spoon</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Plastový odznak</t>
+          <t>Velký plastový tác do restaurace; Lžička na kaviár, plast</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>20, 64</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.63</v>
+        <v>28.04</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>120</v>
+        <v>448.8</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -771,31 +771,31 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4414 90 00</t>
+          <t>3926 90 97 90</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Picture frame S; Picture frame M; Picture frame L; Picture frame XL; Picture frame Oval</t>
+          <t>Pin</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Dřevěný rámeček na obrazy S; Dřevěný rámeček na obrazy M; Dřevěný rámeček na obrazy L; Dřevěný rámeček na obrazy XL; Dřevěný rámeček na obrazy oválný</t>
+          <t>Plastový odznak</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>39, 40, 41, 42, 43</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="I12" s="6" t="n">
-        <v>117</v>
+        <v>0.63</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>1375</v>
+        <v>120</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -818,7 +818,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO. Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -828,22 +832,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>4419 90 00</t>
+          <t>4414 90 00</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Round wooden bread</t>
+          <t>Picture frame S; Picture frame M; Picture frame L; Picture frame XL; Picture frame Oval</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Kulaté dřevěné prkénko na chléb</t>
+          <t>Dřevěný rámeček na obrazy S; Dřevěný rámeček na obrazy M; Dřevěný rámeček na obrazy L; Dřevěný rámeček na obrazy XL; Dřevěný rámeček na obrazy oválný</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39, 40, 41, 42, 43</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -852,7 +856,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -860,10 +864,10 @@
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>760</v>
+        <v>1375</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -885,31 +889,31 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>4421 91 00</t>
+          <t>4419 20 90 00</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Toothpick</t>
+          <t>Round wooden bread</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Bambusová párátka (krabička)</t>
+          <t>Prkénko servírovací na chléb, kulaté, rubber wood</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -917,10 +921,10 @@
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>69</v>
+        <v>760</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -932,7 +936,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -942,31 +950,31 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>4819 10 00</t>
+          <t>4421 91 00 00</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Shot glass souvernir box</t>
+          <t>Toothpick</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Papírová dárková krabička na panáky</t>
+          <t>Bambusová párátka</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -974,10 +982,10 @@
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -989,7 +997,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -999,22 +1011,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>4819 20 00</t>
+          <t>4819 20 00 00</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Take away burger box; Take away steak box S; Take away steak box M; Take away steak box L; Steakknives souvenir box</t>
+          <t>Take away burger box; Take away steak box S; Take away steak box M; Take away steak box L; Shot glass souvernir box; Steakknives souvenir box</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Papírová krabička na burger; Papírová krabice na steak S (potištěná); Papírová krabice na steak M (potištěná); Papírová krabice na steak L (potištěná); Papírová dárková krabička na steakové nože</t>
+          <t>Skládací krabička na burgery; Skládací krabice na steak S, potištěná; Skládací krabice na steak M, potištěná; Skládací krabice na steak L, potištěná; Papírová dárková krabička na panáky; Papírová dárková krabička na steakové nože</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>6, 7, 8, 9, 15</t>
+          <t>6, 7, 8, 9, 14, 15</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1023,7 +1035,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3002</v>
+        <v>3102</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
@@ -1031,10 +1043,10 @@
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1230</v>
+        <v>1256</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>3994.6</v>
+        <v>4224.6</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1113,22 +1125,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>4820 30 00</t>
+          <t>4819 50 00 00</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Bill Holder</t>
+          <t>Take away box 120m; Take away box 210m; Take away box 500m; Take away box 1070m</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Papírové desky na účet</t>
+          <t>Papírová krabička TAKE AWAY 120 ml s papírovým víčkem; Papírová krabička TAKE AWAY 210 ml s papírovým víčkem; Papírová krabička TAKE AWAY 500 ml s papírovým víčkem; Papírová krabička TAKE AWAY 1070 ml s papírovým víčkem</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2, 3, 4, 5</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1137,7 +1149,7 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>500</v>
+        <v>8100</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
@@ -1145,10 +1157,10 @@
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>100</v>
+        <v>1840</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1160,7 +1172,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1170,22 +1186,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>4823 69 90</t>
+          <t>4820 30 00</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Take away box 120m; Take away box 210m; Take away box 500m; Take away box 1070m</t>
+          <t>Bill Holder</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Papírová miska 120 ml s papírovým víčkem; Papírová miska 210 ml s papírovým víčkem; Papírová miska 500 ml s papírovým víčkem; Papírová miska 1070 ml s papírovým víčkem</t>
+          <t>Papírové desky na účet</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2, 3, 4, 5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1194,7 +1210,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>8100</v>
+        <v>500</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
@@ -1202,10 +1218,10 @@
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1840</v>
+        <v>100</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1227,22 +1243,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>4823 70 90</t>
+          <t>4823 70 90 00</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Take away box 2oz</t>
+          <t>Take away box 2oz; Coaster</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Jednorázový kelímek 2 oz z bagasy</t>
+          <t>Kelímek 2 oz z bagasy (lisovaná papírovina); Papírový tácek pod sklenici s logem EG</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1, 65</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1251,7 +1267,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
@@ -1259,10 +1275,10 @@
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1274,7 +1290,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1284,22 +1304,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>4823 90 85</t>
+          <t>4823 90 85 80</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Coaster</t>
+          <t>Paper Flags all kinds</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Papírový tácek pod sklenici</t>
+          <t>Papírové vlaječky</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1308,7 +1328,7 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>500</v>
+        <v>63000</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
@@ -1316,10 +1336,10 @@
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>50</v>
+        <v>1260</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1331,7 +1351,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1341,31 +1365,31 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>4911 99 00</t>
+          <t>6105 10 00</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Paper Flags all kinds</t>
+          <t>Polo; Polo Long Sleeve</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Papírové vlaječky různé</t>
+          <t>Polokošile; Polokošile s dlouhým rukávem</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>67, 69</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>63000</v>
+        <v>543</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1373,10 +1397,10 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>24</v>
+        <v>182</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1260</v>
+        <v>4445</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1398,22 +1422,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>6105 10 00</t>
+          <t>6109 10 00</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Polo; Polo Long Sleeve</t>
+          <t>T-Shirt</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Polokošile; Polokošile s dlouhým rukávem</t>
+          <t>Tričko</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>67, 69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1422,7 +1446,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>543</v>
+        <v>245</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
@@ -1430,10 +1454,10 @@
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>4445</v>
+        <v>1715</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1455,22 +1479,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>6109 10 00</t>
+          <t>6203 42 35</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>T-Shirt</t>
+          <t>Trouser</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Tričko</t>
+          <t>Kalhoty dlouhé</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1479,7 +1503,7 @@
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>245</v>
+        <v>63</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
@@ -1487,10 +1511,10 @@
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1715</v>
+        <v>945</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1512,22 +1536,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>6203 42 35</t>
+          <t>6205 20 00</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Trouser</t>
+          <t>Floor Uniform - Men</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Kalhoty dlouhé</t>
+          <t>Pánská košile – uniforma obsluhy</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1536,7 +1560,7 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>63</v>
+        <v>411</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1544,10 +1568,10 @@
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>945</v>
+        <v>3699</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1569,22 +1593,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>6205 20 00</t>
+          <t>6206 30 00</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Floor Uniform - Men</t>
+          <t>Floor Uniform - Women</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Pánská košile – uniforma obsluhy</t>
+          <t>Dámská košile – uniforma obsluhy</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1593,7 +1617,7 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>411</v>
+        <v>337</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1601,10 +1625,10 @@
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3699</v>
+        <v>3033</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1626,22 +1650,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>6206 30 00</t>
+          <t>6211 32 10</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Floor Uniform - Women</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Dámská košile – uniforma obsluhy</t>
+          <t>Kuchařský rondon</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1650,7 +1674,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -1658,10 +1682,10 @@
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3033</v>
+        <v>7291</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -1683,22 +1707,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>6211 32 10</t>
+          <t>6211 43 10</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Apron</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Kuchařský rondon</t>
+          <t>Zástěra</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1707,7 +1731,7 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>317</v>
+        <v>154</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1715,10 +1739,10 @@
         </is>
       </c>
       <c r="I28" s="6" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>7291</v>
+        <v>1386</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
@@ -1740,22 +1764,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>6211 43 10</t>
+          <t>6215 20 00</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Apron</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Zástěra</t>
+          <t>Kravata</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1764,7 +1788,7 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -1772,10 +1796,10 @@
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>1386</v>
+        <v>450</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
@@ -1787,7 +1811,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1797,22 +1825,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>6215 20 00</t>
+          <t>6216 00 00</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Hot Plate Glove</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Kravata</t>
+          <t>Chňapka / rukavice na horké talíře (pár)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1821,7 +1849,7 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -1829,10 +1857,10 @@
         </is>
       </c>
       <c r="I30" s="6" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>450</v>
+        <v>39</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -1858,22 +1886,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>6216 00 00</t>
+          <t>6302 51 00 90</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Hot Plate Glove</t>
+          <t>Napkin fabric set up</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Chňapka / rukavice na horké talíře (pár)</t>
+          <t>Stolní ubrousky, bavlněná tkanina</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1882,7 +1910,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>30</v>
+        <v>2000</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -1890,10 +1918,10 @@
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2.15</v>
+        <v>122</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>39</v>
+        <v>7200</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -1907,7 +1935,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
@@ -1919,22 +1947,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>6302 51 00</t>
+          <t>6302 60 00</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Napkin fabric set up</t>
+          <t>Black Towel</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Látkový ubrousek</t>
+          <t>Černý ručník</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1943,7 +1971,7 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1951,10 +1979,10 @@
         </is>
       </c>
       <c r="I32" s="6" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>7200</v>
+        <v>500</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -1976,22 +2004,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>6302 60 00</t>
+          <t>6505 00 30</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Black Towel</t>
+          <t>Cap</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Černý ručník</t>
+          <t>Kšiltovka</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2000,7 +2028,7 @@
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -2008,10 +2036,10 @@
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
@@ -2023,7 +2051,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2033,31 +2065,31 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>6505 00 30</t>
+          <t>6912 00 25 10</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>FF-bowl big; Side dish bowl &amp; cover; Sauce bowl; Medium plate; Milk jug; Sugar jug  small one; Dressing  jug small one</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Kšiltovka</t>
+          <t>Velká miska salátová, keramika; Přílohová mistička s pokličkou, keramika; Miska na omáčku, keramika; Keramický talíř střední; Malá konvička na mléko, keramika; Malá dóza na cukr, keramika; Malá dóza na omáčky, keramika</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>17, 18, 19, 25, 27, 28, 29</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Ceramic</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>50</v>
+        <v>670</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -2065,24 +2097,24 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2</v>
+        <v>250.96</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>150</v>
+        <v>1684</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>AD clo na keramické nádobí platí jen při původu ČLR – ověřit, že původ je VN.</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2094,31 +2126,31 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>6911 10 00</t>
+          <t>7010 90 43</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>FF-bowl big; Side dish bowl &amp; cover; Sauce bowl; Medium plate; Milk jug; Sugar jug  small one; Dressing  jug small one</t>
+          <t>Vodka bottle</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Velká keramická mísa; Keramická miska na přílohy s víčkem; Keramická miska na omáčku; Keramický talíř střední; Keramická konvička na mléko; Keramická cukřenka malá; Keramická konvička na dresink malá</t>
+          <t>Skleněná láhev na vodku (prázdná)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>17, 18, 19, 25, 27, 28, 29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Ceramic</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>670</v>
+        <v>1368</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -2126,26 +2158,22 @@
         </is>
       </c>
       <c r="I35" s="6" t="n">
-        <v>250.96</v>
+        <v>860.5</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1684</v>
+        <v>2736</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>AD clo na keramické nádobí platí jen při původu ČLR – ověřit, že původ je VN.</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
-        </is>
-      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2155,31 +2183,31 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>7010 90 43</t>
+          <t>7117 19 00</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Vodka bottle</t>
+          <t>Clip</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Skleněná láhev na vodku (prázdná)</t>
+          <t>Kovová spona na kravatu</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1368</v>
+        <v>100</v>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
@@ -2187,10 +2215,10 @@
         </is>
       </c>
       <c r="I36" s="6" t="n">
-        <v>860.5</v>
+        <v>1.37</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>2736</v>
+        <v>260</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -2202,7 +2230,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2212,27 +2244,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>7117 19 00</t>
+          <t>7323 93 00 90</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Clip</t>
+          <t>Paricha; Paricha plate Small; Paricha plate big</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Kovová spona na kravatu</t>
+          <t>Nerezová pánev na uhlíky na udržení teplého masa (parrilla); Nerezový talíř na parrillu malý; Nerezový talíř na parrillu velký</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>36, 37, 38</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Stainless steel</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -2244,10 +2276,10 @@
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1.37</v>
+        <v>38</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
@@ -2261,7 +2293,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2273,31 +2305,31 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>7323 93 10</t>
+          <t>7323 99 00</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Paricha; Paricha plate Small; Paricha plate big</t>
+          <t>Astray</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Nerezový servírovací tác s držadlem (parrilla); Nerezový talíř na parrillu malý; Nerezový talíř na parrillu velký</t>
+          <t>Kovový popelník</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>36, 37, 38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Stainless steel</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -2305,10 +2337,10 @@
         </is>
       </c>
       <c r="I38" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>440</v>
+        <v>4680</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
@@ -2322,7 +2354,7 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2334,31 +2366,31 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>7323 99 00</t>
+          <t>8211 91 00</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Astray</t>
+          <t>Steak knives; Setup Knife</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Kovový popelník</t>
+          <t>Nerezový steakový nůž; Nerezový jídelní nůž</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24, 47</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Stainless steel</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -2366,10 +2398,10 @@
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>35</v>
+        <v>108.82</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4680</v>
+        <v>5660</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
@@ -2383,7 +2415,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2395,22 +2427,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>8211 91 00</t>
+          <t>8215 99 10 00</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Steak knives; Setup Knife</t>
+          <t>Salsa spoon espresso; Capucino spoon sauce; Setup folk; Latte spoon; Dessert Spoon; Dessert Fork; Small spoon</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Nerezový steakový nůž; Nerezový jídelní nůž</t>
+          <t>Lžička na espresso, nerez; Lžička na cappuccino, nerez; Vidlička, nerez; Lžička na latte, nerez; Dezertní lžička, nerez; Dezertní vidlička, nerez; Malá lžička, nerez</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>24, 47</t>
+          <t>21, 22, 23, 55, 56, 57, 58</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2419,7 +2451,7 @@
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -2427,10 +2459,10 @@
         </is>
       </c>
       <c r="I40" s="6" t="n">
-        <v>108.82</v>
+        <v>37.03</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>5660</v>
+        <v>672</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
@@ -2444,7 +2476,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2456,31 +2488,31 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>8215 99 10</t>
+          <t>8310 00 00</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Salsa spoon espresso; Capucino spoon sauce; Setup folk; Latte spoon; Dessert Spoon; Dessert Fork; Small spoon</t>
+          <t>Round sign; Butcher sign</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Nerezová lžička na espresso / salsu; Nerezová lžička na cappuccino / omáčku; Nerezová jídelní vidlička; Nerezová lžička na latte; Nerezová dezertní lžička; Nerezová dezertní vidlička; Nerezová malá lžička</t>
+          <t>Kulatá reklamní cedule (kov, plast, nerez); Cedule 'Butcher' (kov, plast, nerez)</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>21, 22, 23, 55, 56, 57, 58</t>
+          <t>50, 54</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Stainless steel</t>
+          <t>Metal, plastic and stainless steel</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1320</v>
+        <v>7</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -2488,10 +2520,10 @@
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>37.03</v>
+        <v>126</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>672</v>
+        <v>2140</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
@@ -2505,7 +2537,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2517,31 +2549,31 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>8310 00 00</t>
+          <t>8438 10 10</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Round sign; Butcher sign</t>
+          <t>Proofer</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Kulatá reklamní cedule (kov, plast, nerez); Cedule 'Butcher' (kov, plast, nerez)</t>
+          <t>Kynárna na těsto</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>50, 54</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Metal, plastic and stainless steel</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2549,10 +2581,10 @@
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>126</v>
+        <v>446</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>2140</v>
+        <v>1112</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -2578,31 +2610,31 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>8438 10 10</t>
+          <t>9401 61 00 00</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Proofer</t>
+          <t>Low chair</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Kynárna na těsto</t>
+          <t>Nízká židle do restaurace, mořený buk, čalouněná černou koženkou</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
@@ -2610,10 +2642,10 @@
         </is>
       </c>
       <c r="I43" s="6" t="n">
-        <v>446</v>
+        <v>270</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1112</v>
+        <v>2400</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
@@ -2627,7 +2659,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
@@ -2639,22 +2671,22 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>9401 69 00</t>
+          <t>9403 91 00 90</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Low chair</t>
+          <t>Table face</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Nízká dřevěná židle</t>
+          <t>Stolová deska, dub mořený</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2663,7 +2695,7 @@
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
@@ -2671,10 +2703,10 @@
         </is>
       </c>
       <c r="I44" s="6" t="n">
-        <v>270</v>
+        <v>432</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2400</v>
+        <v>2808</v>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
@@ -2686,7 +2718,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2696,27 +2732,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>9403 91 00</t>
+          <t>9403 99 10 90</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Table face</t>
+          <t>Low table leg</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Dřevěná stolní deska</t>
+          <t>Kovová noha od stolu nízká</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
@@ -2728,10 +2764,10 @@
         </is>
       </c>
       <c r="I45" s="6" t="n">
-        <v>432</v>
+        <v>600</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2808</v>
+        <v>888</v>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
@@ -2745,7 +2781,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2757,31 +2793,31 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>9403 99 10</t>
+          <t>9405 21 40 00</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Low table leg</t>
+          <t>Table lamp</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Kovová podnož nízkého stolu</t>
+          <t>Stolní lampička, LED, USB nabíjení</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
@@ -2789,11 +2825,11 @@
         </is>
       </c>
       <c r="I46" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J46" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>888</v>
-      </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
@@ -2806,95 +2842,38 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>GAUCHO COMPANY LIMITED (HCMC, VN)</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>9405 21 40</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Table lamp</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>Stolní LED lampa (plast)</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="I48" s="11">
-        <f>SUM(I10:I47)</f>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>CHYBÍ</t>
+        </is>
+      </c>
+      <c r="I47" s="11">
+        <f>SUM(I10:I46)</f>
         <v/>
       </c>
-      <c r="J48" s="11">
-        <f>SUM(J10:J47)</f>
+      <c r="J47" s="11">
+        <f>SUM(J10:J46)</f>
         <v/>
       </c>
-      <c r="K48" s="9" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/HS_Code_Summary_EL_GAUCHO_CZ_GAUCHO05.xlsx
+++ b/output/HS_Code_Summary_EL_GAUCHO_CZ_GAUCHO05.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Polo; Polo Long Sleeve</t>
+          <t>Polo; Polo Long Sleeve; Floor Uniform - Men</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Polokošile; Polokošile s dlouhým rukávem</t>
+          <t>Polokošile; Polokošile s dlouhým rukávem; Pánská košile – uniforma obsluhy</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>67, 69</t>
+          <t>67, 69, 71</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>543</v>
+        <v>954</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>4445</v>
+        <v>8144</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>6205 20 00</t>
+          <t>6206 30 00</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Floor Uniform - Men</t>
+          <t>Floor Uniform - Women</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Pánská košile – uniforma obsluhy</t>
+          <t>Dámská košile – uniforma obsluhy</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>411</v>
+        <v>337</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>3699</v>
+        <v>3033</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1593,22 +1593,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>6206 30 00</t>
+          <t>6211 32 10</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Floor Uniform - Women</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Dámská košile – uniforma obsluhy</t>
+          <t>Kuchařský rondon</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3033</v>
+        <v>7291</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1650,22 +1650,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>6211 32 10</t>
+          <t>6211 43 10</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Apron</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Kuchařský rondon</t>
+          <t>Zástěra</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>317</v>
+        <v>154</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>144</v>
+        <v>24</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>7291</v>
+        <v>1386</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -1707,22 +1707,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>6211 43 10</t>
+          <t>6215 20 00</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Apron</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Zástěra</t>
+          <t>Kravata</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="I28" s="6" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1386</v>
+        <v>450</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
@@ -1754,7 +1754,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1764,22 +1768,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>6215 20 00</t>
+          <t>6216 00 00</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Hot Plate Glove</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Kravata</t>
+          <t>Chňapka / rukavice na horké talíře (pár)</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1788,7 +1792,7 @@
         </is>
       </c>
       <c r="G29" s="4" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -1796,10 +1800,10 @@
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>450</v>
+        <v>39</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
@@ -1825,22 +1829,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>6216 00 00</t>
+          <t>6302 51 00 90</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Hot Plate Glove</t>
+          <t>Napkin fabric set up</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Chňapka / rukavice na horké talíře (pár)</t>
+          <t>Stolní ubrousky, bavlněná tkanina</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1849,7 +1853,7 @@
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>30</v>
+        <v>2000</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -1857,10 +1861,10 @@
         </is>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2.15</v>
+        <v>122</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>39</v>
+        <v>7200</v>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
@@ -1886,22 +1890,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>6302 51 00 90</t>
+          <t>6302 60 00</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Napkin fabric set up</t>
+          <t>Black Towel</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Stolní ubrousky, bavlněná tkanina</t>
+          <t>Černý ručník</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1910,7 +1914,7 @@
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -1918,10 +1922,10 @@
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>7200</v>
+        <v>500</v>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
@@ -1933,11 +1937,7 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Kód dle minulého proclení GAUCHO.</t>
-        </is>
-      </c>
+      <c r="M31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1947,22 +1947,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>6302 60 00</t>
+          <t>6505 00 30</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Black Towel</t>
+          <t>Cap</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Černý ručník</t>
+          <t>Kšiltovka</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="I32" s="6" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
@@ -1994,7 +1994,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2004,31 +2008,31 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>6505 00 30</t>
+          <t>6912 00 25 10</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>FF-bowl big; Side dish bowl &amp; cover; Sauce bowl; Medium plate; Milk jug; Sugar jug  small one; Dressing  jug small one</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Kšiltovka</t>
+          <t>Velká miska salátová, keramika; Přílohová mistička s pokličkou, keramika; Miska na omáčku, keramika; Keramický talíř střední; Malá konvička na mléko, keramika; Malá dóza na cukr, keramika; Malá dóza na omáčky, keramika</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>17, 18, 19, 25, 27, 28, 29</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Fabric</t>
+          <t>Ceramic</t>
         </is>
       </c>
       <c r="G33" s="4" t="n">
-        <v>50</v>
+        <v>670</v>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
@@ -2036,24 +2040,24 @@
         </is>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2</v>
+        <v>250.96</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>150</v>
+        <v>1684</v>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>AD clo na keramické nádobí platí jen při původu ČLR – ověřit, že původ je VN.</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2065,31 +2069,31 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>6912 00 25 10</t>
+          <t>7010 90 43</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>FF-bowl big; Side dish bowl &amp; cover; Sauce bowl; Medium plate; Milk jug; Sugar jug  small one; Dressing  jug small one</t>
+          <t>Vodka bottle</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Velká miska salátová, keramika; Přílohová mistička s pokličkou, keramika; Miska na omáčku, keramika; Keramický talíř střední; Malá konvička na mléko, keramika; Malá dóza na cukr, keramika; Malá dóza na omáčky, keramika</t>
+          <t>Skleněná láhev na vodku (prázdná)</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>17, 18, 19, 25, 27, 28, 29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Ceramic</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>670</v>
+        <v>1368</v>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
@@ -2097,26 +2101,22 @@
         </is>
       </c>
       <c r="I34" s="6" t="n">
-        <v>250.96</v>
+        <v>860.5</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>1684</v>
+        <v>2736</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>AD clo na keramické nádobí platí jen při původu ČLR – ověřit, že původ je VN.</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Kód dle minulého proclení GAUCHO. Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
-        </is>
-      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2126,31 +2126,31 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>7010 90 43</t>
+          <t>7117 19 00</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Vodka bottle</t>
+          <t>Clip</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Skleněná láhev na vodku (prázdná)</t>
+          <t>Kovová spona na kravatu</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1368</v>
+        <v>100</v>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="I35" s="6" t="n">
-        <v>860.5</v>
+        <v>1.37</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>2736</v>
+        <v>260</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
@@ -2173,7 +2173,11 @@
           <t>Ne</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2183,27 +2187,27 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>7117 19 00</t>
+          <t>7323 93 00 90</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Clip</t>
+          <t>Paricha; Paricha plate Small; Paricha plate big</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Kovová spona na kravatu</t>
+          <t>Nerezová pánev na uhlíky na udržení teplého masa (parrilla); Nerezový talíř na parrillu malý; Nerezový talíř na parrillu velký</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>36, 37, 38</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Stainless steel</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -2215,10 +2219,10 @@
         </is>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1.37</v>
+        <v>38</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2244,31 +2248,31 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>7323 93 00 90</t>
+          <t>7323 99 00</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Paricha; Paricha plate Small; Paricha plate big</t>
+          <t>Astray</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Nerezová pánev na uhlíky na udržení teplého masa (parrilla); Nerezový talíř na parrillu malý; Nerezový talíř na parrillu velký</t>
+          <t>Kovový popelník</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>36, 37, 38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Stainless steel</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
@@ -2276,10 +2280,10 @@
         </is>
       </c>
       <c r="I37" s="6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>440</v>
+        <v>4680</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
@@ -2293,7 +2297,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2305,31 +2309,31 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>7323 99 00</t>
+          <t>8211 91 00</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Astray</t>
+          <t>Steak knives; Setup Knife</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Kovový popelník</t>
+          <t>Nerezový steakový nůž; Nerezový jídelní nůž</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24, 47</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Stainless steel</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>120</v>
+        <v>1200</v>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
@@ -2337,10 +2341,10 @@
         </is>
       </c>
       <c r="I38" s="6" t="n">
-        <v>35</v>
+        <v>108.82</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4680</v>
+        <v>5660</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
@@ -2354,7 +2358,7 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2370,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>8211 91 00</t>
+          <t>8215 99 10 00</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Steak knives; Setup Knife</t>
+          <t>Salsa spoon espresso; Capucino spoon sauce; Setup folk; Latte spoon; Dessert Spoon; Dessert Fork; Small spoon</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Nerezový steakový nůž; Nerezový jídelní nůž</t>
+          <t>Lžička na espresso, nerez; Lžička na cappuccino, nerez; Vidlička, nerez; Lžička na latte, nerez; Dezertní lžička, nerez; Dezertní vidlička, nerez; Malá lžička, nerez</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>24, 47</t>
+          <t>21, 22, 23, 55, 56, 57, 58</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2390,7 +2394,7 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
@@ -2398,10 +2402,10 @@
         </is>
       </c>
       <c r="I39" s="6" t="n">
-        <v>108.82</v>
+        <v>37.03</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>5660</v>
+        <v>672</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
@@ -2415,7 +2419,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
         </is>
       </c>
     </row>
@@ -2427,31 +2431,31 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>8215 99 10 00</t>
+          <t>8310 00 00</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Salsa spoon espresso; Capucino spoon sauce; Setup folk; Latte spoon; Dessert Spoon; Dessert Fork; Small spoon</t>
+          <t>Round sign; Butcher sign</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Lžička na espresso, nerez; Lžička na cappuccino, nerez; Vidlička, nerez; Lžička na latte, nerez; Dezertní lžička, nerez; Dezertní vidlička, nerez; Malá lžička, nerez</t>
+          <t>Kulatá reklamní cedule (kov, plast, nerez); Cedule 'Butcher' (kov, plast, nerez)</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>21, 22, 23, 55, 56, 57, 58</t>
+          <t>50, 54</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Stainless steel</t>
+          <t>Metal, plastic and stainless steel</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1320</v>
+        <v>7</v>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
@@ -2459,10 +2463,10 @@
         </is>
       </c>
       <c r="I40" s="6" t="n">
-        <v>37.03</v>
+        <v>126</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>672</v>
+        <v>2140</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
@@ -2476,7 +2480,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour). Hrubá hmotnost částečně rozpočtena podle hodnoty (sdílený karton).</t>
+          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2488,31 +2492,31 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>8310 00 00</t>
+          <t>8438 10 10</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Round sign; Butcher sign</t>
+          <t>Proofer</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Kulatá reklamní cedule (kov, plast, nerez); Cedule 'Butcher' (kov, plast, nerez)</t>
+          <t>Kynárna na těsto</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>50, 54</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Metal, plastic and stainless steel</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
@@ -2520,10 +2524,10 @@
         </is>
       </c>
       <c r="I41" s="6" t="n">
-        <v>126</v>
+        <v>446</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>2140</v>
+        <v>1112</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
@@ -2549,31 +2553,31 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>8438 10 10</t>
+          <t>9401 61 00 00</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Proofer</t>
+          <t>Low chair</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Kynárna na těsto</t>
+          <t>Nízká židle do restaurace, mořený buk, čalouněná černou koženkou</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
@@ -2581,10 +2585,10 @@
         </is>
       </c>
       <c r="I42" s="6" t="n">
-        <v>446</v>
+        <v>270</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1112</v>
+        <v>2400</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
@@ -2598,7 +2602,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
@@ -2610,22 +2614,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>9401 61 00 00</t>
+          <t>9403 91 00 90</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Low chair</t>
+          <t>Table face</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Nízká židle do restaurace, mořený buk, čalouněná černou koženkou</t>
+          <t>Stolová deska, dub mořený</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2634,7 +2638,7 @@
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
@@ -2642,10 +2646,10 @@
         </is>
       </c>
       <c r="I43" s="6" t="n">
-        <v>270</v>
+        <v>432</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>2400</v>
+        <v>2808</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
@@ -2659,7 +2663,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Kód dle minulého proclení GAUCHO.</t>
+          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
         </is>
       </c>
     </row>
@@ -2671,27 +2675,27 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>9403 91 00 90</t>
+          <t>9403 99 10 90</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Table face</t>
+          <t>Low table leg</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Stolová deska, dub mořený</t>
+          <t>Kovová noha od stolu nízká</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
@@ -2703,10 +2707,10 @@
         </is>
       </c>
       <c r="I44" s="6" t="n">
-        <v>432</v>
+        <v>600</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2808</v>
+        <v>888</v>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
@@ -2732,31 +2736,31 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>9403 99 10 90</t>
+          <t>9405 21 40 00</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Low table leg</t>
+          <t>Table lamp</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Kovová noha od stolu nízká</t>
+          <t>Stolní lampička, LED, USB nabíjení</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
@@ -2764,11 +2768,11 @@
         </is>
       </c>
       <c r="I45" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J45" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="J45" s="6" t="n">
-        <v>888</v>
-      </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Ne</t>
@@ -2781,99 +2785,38 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Kód dle minulého proclení GAUCHO. Ocel/kov: chybí hutní atest (melt &amp; pour).</t>
+          <t>Kód dle minulého proclení GAUCHO.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>GAUCHO COMPANY LIMITED (HCMC, VN)</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>9405 21 40 00</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Table lamp</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Stolní lampička, LED, USB nabíjení</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>600</v>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="inlineStr">
-        <is>
-          <t>Kód dle minulého proclení GAUCHO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="I47" s="11">
-        <f>SUM(I10:I46)</f>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>CHYBÍ</t>
+        </is>
+      </c>
+      <c r="I46" s="11">
+        <f>SUM(I10:I45)</f>
         <v/>
       </c>
-      <c r="J47" s="11">
-        <f>SUM(J10:J46)</f>
+      <c r="J46" s="11">
+        <f>SUM(J10:J45)</f>
         <v/>
       </c>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="9" t="n"/>
+      <c r="M46" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
